--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$70</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2549" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3381" uniqueCount="594">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedProcedure</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedProcedure</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:21:37+00:00</t>
+    <t>2025-03-11T16:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ELGA</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ELGA (https://www.elga.gv.at/)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -511,16 +508,16 @@
     <t>PR1-19</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier</t>
-  </si>
-  <si>
-    <t>MopedConditionIdentifier</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier</t>
+  </si>
+  <si>
+    <t>MopedProcedureIdentifier</t>
   </si>
   <si>
     <t>MOPED Identifier = Aufnahmezahl-Procedure.code-Procedure.occurrence(YYYY-MM-DDTHH:MM)</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.id</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.id</t>
   </si>
   <si>
     <t>Procedure.identifier.id</t>
@@ -542,7 +539,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.extension</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.extension</t>
   </si>
   <si>
     <t>Procedure.identifier.extension</t>
@@ -561,7 +558,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.use</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.use</t>
   </si>
   <si>
     <t>Procedure.identifier.use</t>
@@ -591,7 +588,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type</t>
   </si>
   <si>
     <t>Procedure.identifier.type</t>
@@ -622,19 +619,19 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.id</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.id</t>
   </si>
   <si>
     <t>Procedure.identifier.type.id</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.extension</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.extension</t>
   </si>
   <si>
     <t>Procedure.identifier.type.extension</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.coding</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.coding</t>
   </si>
   <si>
     <t>Procedure.identifier.type.coding</t>
@@ -665,19 +662,19 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.coding.id</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.coding.id</t>
   </si>
   <si>
     <t>Procedure.identifier.type.coding.id</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.coding.extension</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.coding.extension</t>
   </si>
   <si>
     <t>Procedure.identifier.type.coding.extension</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.coding.system</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.coding.system</t>
   </si>
   <si>
     <t>Procedure.identifier.type.coding.system</t>
@@ -704,7 +701,7 @@
     <t>C*E.3</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.coding.version</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.coding.version</t>
   </si>
   <si>
     <t>Procedure.identifier.type.coding.version</t>
@@ -732,7 +729,7 @@
     <t>C*E.7</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.coding.code</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.coding.code</t>
   </si>
   <si>
     <t>Procedure.identifier.type.coding.code</t>
@@ -763,7 +760,7 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.coding.display</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.coding.display</t>
   </si>
   <si>
     <t>Procedure.identifier.type.coding.display</t>
@@ -787,7 +784,7 @@
     <t>C*E.2 - but note this is not well followed</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.coding.userSelected</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.coding.userSelected</t>
   </si>
   <si>
     <t>Procedure.identifier.type.coding.userSelected</t>
@@ -818,7 +815,7 @@
     <t>Sometimes implied by being first</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.type.text</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.type.text</t>
   </si>
   <si>
     <t>Procedure.identifier.type.text</t>
@@ -845,7 +842,7 @@
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.system</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.system</t>
   </si>
   <si>
     <t>Procedure.identifier.system</t>
@@ -875,7 +872,7 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.value</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.value</t>
   </si>
   <si>
     <t>Procedure.identifier.value</t>
@@ -906,7 +903,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.period</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.period</t>
   </si>
   <si>
     <t>Procedure.identifier.period</t>
@@ -931,7 +928,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>Procedure.identifier:MopedConditionIdentifier.assigner</t>
+    <t>Procedure.identifier:MopedProcedureIdentifier.assigner</t>
   </si>
   <si>
     <t>Procedure.identifier.assigner</t>
@@ -1128,6 +1125,76 @@
     <t>PR1-6</t>
   </si>
   <si>
+    <t>Procedure.category.id</t>
+  </si>
+  <si>
+    <t>Procedure.category.extension</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe</t>
+  </si>
+  <si>
+    <t>MELGruppe</t>
+  </si>
+  <si>
+    <t>https://elga.moped.at/ValueSet/LKFmedizinischeEinzelleistungen</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.id</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.id</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.extension</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.system</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.system</t>
+  </si>
+  <si>
+    <t>https://elga.moped.at/CodeSystem/LKFmedizinischeEinzelleistungenCS</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.version</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.version</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.code</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.code</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.display</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.display</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding:MELGruppe.userSelected</t>
+  </si>
+  <si>
+    <t>Procedure.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Procedure.category.text</t>
+  </si>
+  <si>
     <t>Procedure.code</t>
   </si>
   <si>
@@ -1135,7 +1202,7 @@
 </t>
   </si>
   <si>
-    <t>Identification of the procedure</t>
+    <t>Leistungskatalog BMSGPK</t>
   </si>
   <si>
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
@@ -1144,7 +1211,10 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-LKFmedizinischeEinzelleistungen-valueset</t>
+    <t>A code to identify a specific procedure .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1157,6 +1227,45 @@
   </si>
   <si>
     <t>PR1-3</t>
+  </si>
+  <si>
+    <t>Procedure.code.id</t>
+  </si>
+  <si>
+    <t>Procedure.code.extension</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding</t>
+  </si>
+  <si>
+    <t>https://elga.moped.at/ValueSet/LKFLeistungskatalog</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.id</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.system</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/lkat-bmsgpk-2025</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.version</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.code</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.display</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Procedure.code.text</t>
   </si>
   <si>
     <t>Procedure.subject</t>
@@ -1204,7 +1313,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedEncounter)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedEncounter)
 </t>
   </si>
   <si>
@@ -1404,7 +1513,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedOrganizationAbteilung)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedOrganizationAbteilung)
 </t>
   </si>
   <si>
@@ -1877,21 +1986,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2065,12 +2159,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN70"/>
+  <dimension ref="A1:AN93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="66.8828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="67.45703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.09765625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.2109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="24.78515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2093,7 +2187,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.0546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.4140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2231,7 +2325,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2343,7 +2437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -2457,7 +2551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -2569,7 +2663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -2683,7 +2777,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -2797,7 +2891,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2911,7 +3005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -3025,7 +3119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>133</v>
       </c>
@@ -3139,7 +3233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>141</v>
       </c>
@@ -3255,7 +3349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -3369,7 +3463,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>158</v>
       </c>
@@ -3487,7 +3581,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -3599,7 +3693,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -3713,7 +3807,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>174</v>
       </c>
@@ -3829,7 +3923,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>184</v>
       </c>
@@ -3943,7 +4037,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>194</v>
       </c>
@@ -4055,7 +4149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>196</v>
       </c>
@@ -4169,7 +4263,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>198</v>
       </c>
@@ -4285,7 +4379,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>208</v>
       </c>
@@ -4397,7 +4491,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>210</v>
       </c>
@@ -4511,7 +4605,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>212</v>
       </c>
@@ -4627,7 +4721,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>221</v>
       </c>
@@ -4741,7 +4835,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>230</v>
       </c>
@@ -4855,7 +4949,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>240</v>
       </c>
@@ -4969,7 +5063,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>248</v>
       </c>
@@ -5085,7 +5179,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>258</v>
       </c>
@@ -5201,7 +5295,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>267</v>
       </c>
@@ -5317,7 +5411,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>277</v>
       </c>
@@ -5431,7 +5525,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>287</v>
       </c>
@@ -5543,7 +5637,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>295</v>
       </c>
@@ -5657,7 +5751,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>304</v>
       </c>
@@ -5769,7 +5863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>310</v>
       </c>
@@ -5883,7 +5977,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>315</v>
       </c>
@@ -5995,7 +6089,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>322</v>
       </c>
@@ -6109,7 +6203,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>331</v>
       </c>
@@ -6223,7 +6317,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>340</v>
       </c>
@@ -6337,7 +6431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>350</v>
       </c>
@@ -6449,7 +6543,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>358</v>
       </c>
@@ -6458,37 +6552,35 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>360</v>
+        <v>163</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>361</v>
+        <v>164</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>362</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6512,11 +6604,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6534,7 +6628,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>358</v>
+        <v>165</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6543,41 +6637,41 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>364</v>
+        <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>365</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>366</v>
+        <v>167</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>367</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>369</v>
+        <v>134</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6586,18 +6680,20 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>370</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>371</v>
+        <v>136</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6634,51 +6730,51 @@
         <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>173</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>375</v>
+        <v>167</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>376</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6689,7 +6785,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6701,16 +6797,20 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>378</v>
+        <v>200</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>379</v>
+        <v>201</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6746,25 +6846,23 @@
         <v>20</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>377</v>
+        <v>205</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
@@ -6776,29 +6874,31 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>87</v>
@@ -6813,18 +6913,20 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>382</v>
+        <v>200</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>383</v>
+        <v>201</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>384</v>
+        <v>202</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6848,13 +6950,11 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6872,13 +6972,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>381</v>
+        <v>205</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -6887,24 +6987,24 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>387</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>388</v>
+        <v>206</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>389</v>
+        <v>207</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6912,7 +7012,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>87</v>
@@ -6924,20 +7024,18 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>391</v>
+        <v>89</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>392</v>
+        <v>163</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6986,7 +7084,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>165</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6995,41 +7093,41 @@
         <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>395</v>
+        <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>397</v>
+        <v>167</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>398</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7038,18 +7136,20 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>400</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>401</v>
+        <v>136</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7086,51 +7186,51 @@
         <v>20</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>399</v>
+        <v>173</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>403</v>
+        <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>404</v>
+        <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>405</v>
+        <v>167</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7138,7 +7238,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>87</v>
@@ -7153,16 +7253,20 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>407</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>408</v>
+        <v>214</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7171,7 +7275,7 @@
         <v>20</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>20</v>
@@ -7210,7 +7314,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7228,25 +7332,25 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>411</v>
+        <v>219</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>413</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7265,18 +7369,18 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>414</v>
+        <v>223</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>415</v>
+        <v>224</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7324,7 +7428,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>412</v>
+        <v>227</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7339,24 +7443,24 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>420</v>
+        <v>228</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>421</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7367,7 +7471,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7379,16 +7483,18 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>422</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>423</v>
+        <v>232</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>424</v>
+        <v>233</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7436,39 +7542,39 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>421</v>
+        <v>236</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>425</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>426</v>
+        <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>427</v>
+        <v>238</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>428</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>428</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7488,19 +7594,21 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>223</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7548,7 +7656,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>165</v>
+        <v>245</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7557,10 +7665,10 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>166</v>
+        <v>237</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7569,29 +7677,29 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>20</v>
+        <v>247</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>429</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>429</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7600,21 +7708,23 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>136</v>
+        <v>251</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7662,19 +7772,19 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>173</v>
+        <v>255</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -7683,53 +7793,53 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>167</v>
+        <v>256</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>20</v>
+        <v>257</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>431</v>
+        <v>20</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>432</v>
+        <v>260</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>433</v>
+        <v>261</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>144</v>
+        <v>263</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7778,19 +7888,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>434</v>
+        <v>264</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -7799,26 +7909,26 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>132</v>
+        <v>265</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>20</v>
+        <v>382</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>87</v>
@@ -7836,14 +7946,14 @@
         <v>186</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>436</v>
+        <v>383</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>437</v>
+        <v>384</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>438</v>
+        <v>385</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7871,10 +7981,10 @@
         <v>345</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>439</v>
+        <v>386</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>440</v>
+        <v>387</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7892,7 +8002,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7907,24 +8017,24 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>441</v>
+        <v>388</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>20</v>
+        <v>389</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>442</v>
+        <v>390</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>443</v>
+        <v>391</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>444</v>
+        <v>392</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>444</v>
+        <v>392</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7932,7 +8042,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>87</v>
@@ -7944,21 +8054,19 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>445</v>
+        <v>89</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>446</v>
+        <v>163</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>447</v>
+        <v>164</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>448</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
       </c>
@@ -8006,50 +8114,50 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>444</v>
+        <v>165</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>449</v>
+        <v>166</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>450</v>
+        <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>451</v>
+        <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>452</v>
+        <v>167</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>453</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>454</v>
+        <v>393</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>454</v>
+        <v>393</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8061,20 +8169,18 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>455</v>
+        <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>456</v>
+        <v>136</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>457</v>
+        <v>170</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8110,31 +8216,31 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>454</v>
+        <v>173</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>449</v>
+        <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8143,18 +8249,18 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>460</v>
+        <v>167</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>461</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>461</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8165,7 +8271,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8174,19 +8280,23 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>289</v>
+        <v>200</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>462</v>
+        <v>201</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -8210,13 +8320,11 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>20</v>
+        <v>395</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8234,13 +8342,13 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>461</v>
+        <v>205</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
@@ -8255,18 +8363,18 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>464</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>464</v>
+        <v>396</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8286,16 +8394,16 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>465</v>
+        <v>89</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>466</v>
+        <v>163</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>467</v>
+        <v>164</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8346,7 +8454,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>464</v>
+        <v>165</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8355,34 +8463,34 @@
         <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>468</v>
+        <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>469</v>
+        <v>167</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>470</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>397</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8398,19 +8506,19 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>472</v>
+        <v>135</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>473</v>
+        <v>136</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>474</v>
+        <v>170</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>475</v>
+        <v>138</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8436,31 +8544,31 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>476</v>
+        <v>20</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>477</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>471</v>
+        <v>173</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8472,27 +8580,27 @@
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>478</v>
+        <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>480</v>
+        <v>167</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>481</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>398</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>398</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8503,7 +8611,7 @@
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8515,18 +8623,20 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>186</v>
+        <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>483</v>
+        <v>214</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>484</v>
+        <v>215</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
       </c>
@@ -8535,7 +8645,7 @@
         <v>20</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>20</v>
+        <v>399</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>20</v>
@@ -8550,13 +8660,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>486</v>
+        <v>20</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>487</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8574,13 +8684,13 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>482</v>
+        <v>218</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
@@ -8595,18 +8705,18 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>488</v>
+        <v>219</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>489</v>
+        <v>220</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8629,16 +8739,16 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>491</v>
+        <v>224</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>492</v>
+        <v>225</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>493</v>
+        <v>226</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8664,13 +8774,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>494</v>
+        <v>20</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>495</v>
+        <v>20</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8688,7 +8798,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>490</v>
+        <v>227</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8709,18 +8819,18 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>496</v>
+        <v>228</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>497</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>497</v>
+        <v>401</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8731,7 +8841,7 @@
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8740,21 +8850,21 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>498</v>
+        <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>499</v>
+        <v>232</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
       </c>
@@ -8802,16 +8912,16 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>497</v>
+        <v>236</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>99</v>
@@ -8823,18 +8933,18 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>502</v>
+        <v>238</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>503</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>503</v>
+        <v>402</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8845,7 +8955,7 @@
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -8854,21 +8964,21 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>504</v>
+        <v>223</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>505</v>
+        <v>242</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8892,13 +9002,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>508</v>
+        <v>20</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>509</v>
+        <v>20</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -8916,16 +9026,16 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>503</v>
+        <v>245</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
@@ -8937,18 +9047,18 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>510</v>
+        <v>246</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>20</v>
+        <v>247</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>511</v>
+        <v>403</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>511</v>
+        <v>403</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8959,7 +9069,7 @@
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8968,19 +9078,23 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>186</v>
+        <v>250</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>512</v>
+        <v>251</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
@@ -9004,13 +9118,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>514</v>
+        <v>20</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>515</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9028,13 +9142,13 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>511</v>
+        <v>255</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
@@ -9049,18 +9163,18 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>516</v>
+        <v>256</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>20</v>
+        <v>257</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>517</v>
+        <v>404</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>517</v>
+        <v>404</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9071,7 +9185,7 @@
         <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9080,19 +9194,23 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>518</v>
+        <v>223</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>519</v>
+        <v>260</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
       </c>
@@ -9140,13 +9258,13 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>517</v>
+        <v>264</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
@@ -9155,35 +9273,35 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>522</v>
+        <v>265</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>523</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>524</v>
+        <v>405</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>524</v>
+        <v>405</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>20</v>
+        <v>406</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9192,16 +9310,16 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>525</v>
+        <v>408</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>526</v>
+        <v>409</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9252,13 +9370,13 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>524</v>
+        <v>405</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
@@ -9267,24 +9385,24 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>20</v>
+        <v>410</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>20</v>
+        <v>411</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>527</v>
+        <v>412</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>528</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>528</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9304,16 +9422,16 @@
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>223</v>
+        <v>415</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>163</v>
+        <v>416</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>164</v>
+        <v>417</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9364,7 +9482,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>165</v>
+        <v>414</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9373,41 +9491,41 @@
         <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>20</v>
+        <v>411</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>529</v>
+        <v>418</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>529</v>
+        <v>418</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9416,19 +9534,19 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>419</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>136</v>
+        <v>420</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>170</v>
+        <v>421</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>138</v>
+        <v>422</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9478,75 +9596,73 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>173</v>
+        <v>418</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>167</v>
+        <v>425</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>20</v>
+        <v>426</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>530</v>
+        <v>427</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>530</v>
+        <v>427</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>431</v>
+        <v>20</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>428</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>20</v>
       </c>
@@ -9594,39 +9710,39 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AG66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="AN66" t="s" s="2">
-        <v>20</v>
+        <v>435</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>531</v>
+        <v>436</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>531</v>
+        <v>436</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9646,16 +9762,16 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>186</v>
+        <v>437</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>532</v>
+        <v>438</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>533</v>
+        <v>439</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9682,13 +9798,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>534</v>
+        <v>20</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>535</v>
+        <v>20</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>536</v>
+        <v>20</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -9706,7 +9822,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>531</v>
+        <v>436</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9721,24 +9837,24 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>20</v>
+        <v>440</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>20</v>
+        <v>441</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>537</v>
+        <v>442</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>538</v>
+        <v>443</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>538</v>
+        <v>443</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9746,7 +9862,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>87</v>
@@ -9758,16 +9874,16 @@
         <v>20</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>539</v>
+        <v>444</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>540</v>
+        <v>445</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>541</v>
+        <v>446</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9818,10 +9934,10 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>538</v>
+        <v>443</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>87</v>
@@ -9836,32 +9952,32 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>542</v>
+        <v>448</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>543</v>
+        <v>449</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>543</v>
+        <v>449</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>20</v>
+        <v>450</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -9870,22 +9986,20 @@
         <v>20</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>544</v>
+        <v>451</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>545</v>
+        <v>452</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>548</v>
+        <v>454</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9910,13 +10024,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>549</v>
+        <v>20</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>550</v>
+        <v>20</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9934,13 +10048,13 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>543</v>
+        <v>449</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
@@ -9949,24 +10063,24 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>20</v>
+        <v>455</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>551</v>
+        <v>457</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>552</v>
+        <v>458</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>552</v>
+        <v>458</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9986,16 +10100,16 @@
         <v>20</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>553</v>
+        <v>459</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>554</v>
+        <v>460</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>555</v>
+        <v>461</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10046,7 +10160,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>552</v>
+        <v>458</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10058,40 +10172,2632 @@
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AK74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="M85" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN70">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8291,7 +8291,7 @@
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -257,7 +257,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}moped-externe-Leistung-KH:Wird bei performer.actor eine KHOrganization angegeben so muss sich diese unterscheiden von der referenzierten Krankenanstalt in perfomer.onBehalfOf {null}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}moped-externe-Leistung-KA:Wird bei performer.actor eine KAOrganization angegeben so muss sich diese unterscheiden von der referenzierten Krankenanstalt in perfomer.onBehalfOf {null}</t>
   </si>
   <si>
     <t>Procedure.id</t>
@@ -1078,7 +1078,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedKHOrganisationseinheit|https://elga.moped.at/StructureDefinition/KHOrganization)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedKAOrganisationseinheit|https://elga.moped.at/StructureDefinition/KAOrganization)
 </t>
   </si>
   <si>
@@ -1101,7 +1101,7 @@
     <t>Procedure.performer.onBehalfOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KHOrganization)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/KAOrganization)
 </t>
   </si>
   <si>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -900,7 +900,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedPatient)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedBasisPatientvbPK|https://elga.moped.at/StructureDefinition/MopedBasisPatientKlarname)
 </t>
   </si>
   <si>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
